--- a/Data/EXCEL/Transfer/salemon/202206/6741-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6741-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A44E9633-BBA3-45A3-8A04-45E1DB20049A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ADB8BDA-4403-484F-A8FE-DFF9664FC29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6741-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1218,20 +1218,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="12.625" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="10" width="10.5" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="10.5" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="15" width="10.5" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="11.25" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="14.375" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="12.625" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="12.625" customWidth="1"/>
+    <col min="14" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="12.625" customWidth="1"/>
+    <col min="17" max="17" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1384,749 +1384,749 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C5" s="7">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D5" s="7">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E5" s="7">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F5" s="8">
-        <v>14.5</v>
+        <v>-10</v>
       </c>
       <c r="G5" s="8">
-        <v>11.11</v>
+        <v>-6.9</v>
       </c>
       <c r="H5" s="9">
-        <v>1.01</v>
-      </c>
-      <c r="I5" s="8">
-        <v>8.7899999999999991</v>
-      </c>
-      <c r="J5" s="8">
-        <v>14.5</v>
+        <v>1.03</v>
+      </c>
+      <c r="I5" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="J5" s="10">
+        <v>4.8099999999999996</v>
       </c>
       <c r="K5" s="9">
-        <v>4.75</v>
-      </c>
-      <c r="L5" s="8">
-        <v>20.100000000000001</v>
+        <v>5.78</v>
+      </c>
+      <c r="L5" s="10">
+        <v>17.100000000000001</v>
       </c>
       <c r="M5" s="9">
-        <v>1.01</v>
-      </c>
-      <c r="N5" s="8">
-        <v>8.7899999999999991</v>
-      </c>
-      <c r="O5" s="8">
-        <v>14.5</v>
+        <v>1.03</v>
+      </c>
+      <c r="N5" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="O5" s="10">
+        <v>4.8099999999999996</v>
       </c>
       <c r="P5" s="9">
-        <v>4.75</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>20.100000000000001</v>
+        <v>5.78</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>17.100000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="C6" s="7">
-        <v>130.5</v>
+        <v>145</v>
       </c>
       <c r="D6" s="7">
-        <v>172.5</v>
+        <v>152</v>
       </c>
       <c r="E6" s="7">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F6" s="10">
-        <v>-30.5</v>
+        <v>14.5</v>
       </c>
       <c r="G6" s="10">
-        <v>-18.940000000000001</v>
+        <v>11.11</v>
       </c>
       <c r="H6" s="9">
-        <v>0.92600000000000005</v>
+        <v>1.01</v>
       </c>
       <c r="I6" s="10">
-        <v>-4.12</v>
-      </c>
-      <c r="J6" s="8">
-        <v>28.6</v>
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="J6" s="10">
+        <v>14.5</v>
       </c>
       <c r="K6" s="9">
-        <v>3.75</v>
-      </c>
-      <c r="L6" s="8">
-        <v>21.7</v>
+        <v>4.75</v>
+      </c>
+      <c r="L6" s="10">
+        <v>20.100000000000001</v>
       </c>
       <c r="M6" s="9">
-        <v>0.92600000000000005</v>
+        <v>1.01</v>
       </c>
       <c r="N6" s="10">
-        <v>-4.12</v>
-      </c>
-      <c r="O6" s="8">
-        <v>28.6</v>
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="O6" s="10">
+        <v>14.5</v>
       </c>
       <c r="P6" s="9">
-        <v>3.75</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>21.7</v>
+        <v>4.75</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>20.100000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="C7" s="7">
-        <v>161</v>
+        <v>130.5</v>
       </c>
       <c r="D7" s="7">
-        <v>206</v>
+        <v>172.5</v>
       </c>
       <c r="E7" s="7">
-        <v>150</v>
-      </c>
-      <c r="F7" s="10">
-        <v>-20.5</v>
-      </c>
-      <c r="G7" s="10">
-        <v>-11.29</v>
+        <v>122</v>
+      </c>
+      <c r="F7" s="8">
+        <v>-30.5</v>
+      </c>
+      <c r="G7" s="8">
+        <v>-18.940000000000001</v>
       </c>
       <c r="H7" s="9">
-        <v>0.96599999999999997</v>
+        <v>0.92600000000000005</v>
       </c>
       <c r="I7" s="8">
-        <v>15.3</v>
-      </c>
-      <c r="J7" s="8">
-        <v>19.7</v>
+        <v>-4.12</v>
+      </c>
+      <c r="J7" s="10">
+        <v>28.6</v>
       </c>
       <c r="K7" s="9">
-        <v>2.82</v>
-      </c>
-      <c r="L7" s="8">
-        <v>19.600000000000001</v>
+        <v>3.75</v>
+      </c>
+      <c r="L7" s="10">
+        <v>21.7</v>
       </c>
       <c r="M7" s="9">
-        <v>0.96599999999999997</v>
+        <v>0.92600000000000005</v>
       </c>
       <c r="N7" s="8">
-        <v>15.3</v>
-      </c>
-      <c r="O7" s="8">
-        <v>19.7</v>
+        <v>-4.12</v>
+      </c>
+      <c r="O7" s="10">
+        <v>28.6</v>
       </c>
       <c r="P7" s="9">
-        <v>2.82</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>19.600000000000001</v>
+        <v>3.75</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>21.7</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>249.5</v>
+        <v>182</v>
       </c>
       <c r="C8" s="7">
-        <v>181.5</v>
+        <v>161</v>
       </c>
       <c r="D8" s="7">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="E8" s="7">
-        <v>168</v>
-      </c>
-      <c r="F8" s="10">
-        <v>-58.5</v>
-      </c>
-      <c r="G8" s="10">
-        <v>-24.38</v>
+        <v>150</v>
+      </c>
+      <c r="F8" s="8">
+        <v>-20.5</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-11.29</v>
       </c>
       <c r="H8" s="9">
-        <v>0.83799999999999997</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="I8" s="10">
-        <v>-17.7</v>
-      </c>
-      <c r="J8" s="8">
-        <v>16.5</v>
+        <v>15.3</v>
+      </c>
+      <c r="J8" s="10">
+        <v>19.7</v>
       </c>
       <c r="K8" s="9">
-        <v>1.86</v>
-      </c>
-      <c r="L8" s="8">
+        <v>2.82</v>
+      </c>
+      <c r="L8" s="10">
         <v>19.600000000000001</v>
       </c>
       <c r="M8" s="9">
-        <v>0.83799999999999997</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="N8" s="10">
-        <v>-17.7</v>
-      </c>
-      <c r="O8" s="8">
-        <v>16.5</v>
+        <v>15.3</v>
+      </c>
+      <c r="O8" s="10">
+        <v>19.7</v>
       </c>
       <c r="P8" s="9">
-        <v>1.86</v>
-      </c>
-      <c r="Q8" s="8">
+        <v>2.82</v>
+      </c>
+      <c r="Q8" s="10">
         <v>19.600000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>264</v>
+        <v>249.5</v>
       </c>
       <c r="C9" s="7">
-        <v>240</v>
+        <v>181.5</v>
       </c>
       <c r="D9" s="7">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="E9" s="7">
-        <v>239</v>
-      </c>
-      <c r="F9" s="10">
-        <v>-24</v>
-      </c>
-      <c r="G9" s="10">
-        <v>-9.09</v>
+        <v>168</v>
+      </c>
+      <c r="F9" s="8">
+        <v>-58.5</v>
+      </c>
+      <c r="G9" s="8">
+        <v>-24.38</v>
       </c>
       <c r="H9" s="9">
-        <v>1.02</v>
-      </c>
-      <c r="I9" s="10">
-        <v>-5.47</v>
-      </c>
-      <c r="J9" s="8">
-        <v>22.2</v>
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="I9" s="8">
+        <v>-17.7</v>
+      </c>
+      <c r="J9" s="10">
+        <v>16.5</v>
       </c>
       <c r="K9" s="9">
-        <v>1.02</v>
-      </c>
-      <c r="L9" s="8">
-        <v>22.2</v>
+        <v>1.86</v>
+      </c>
+      <c r="L9" s="10">
+        <v>19.600000000000001</v>
       </c>
       <c r="M9" s="9">
-        <v>1.02</v>
-      </c>
-      <c r="N9" s="10">
-        <v>-5.47</v>
-      </c>
-      <c r="O9" s="8">
-        <v>22.2</v>
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="N9" s="8">
+        <v>-17.7</v>
+      </c>
+      <c r="O9" s="10">
+        <v>16.5</v>
       </c>
       <c r="P9" s="9">
-        <v>1.02</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>22.2</v>
+        <v>1.86</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>19.600000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="C10" s="7">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="D10" s="7">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="E10" s="7">
-        <v>261</v>
-      </c>
-      <c r="F10" s="10">
-        <v>-35.5</v>
-      </c>
-      <c r="G10" s="10">
-        <v>-11.85</v>
+        <v>239</v>
+      </c>
+      <c r="F10" s="8">
+        <v>-24</v>
+      </c>
+      <c r="G10" s="8">
+        <v>-9.09</v>
       </c>
       <c r="H10" s="9">
-        <v>1.08</v>
-      </c>
-      <c r="I10" s="10">
-        <v>-19.7</v>
-      </c>
-      <c r="J10" s="8">
-        <v>14.3</v>
+        <v>1.02</v>
+      </c>
+      <c r="I10" s="8">
+        <v>-5.47</v>
+      </c>
+      <c r="J10" s="10">
+        <v>22.2</v>
       </c>
       <c r="K10" s="9">
-        <v>11.01</v>
-      </c>
-      <c r="L10" s="8">
-        <v>25.8</v>
+        <v>1.02</v>
+      </c>
+      <c r="L10" s="10">
+        <v>22.2</v>
       </c>
       <c r="M10" s="9">
-        <v>1.08</v>
-      </c>
-      <c r="N10" s="10">
-        <v>-19.7</v>
-      </c>
-      <c r="O10" s="8">
-        <v>14.3</v>
+        <v>1.02</v>
+      </c>
+      <c r="N10" s="8">
+        <v>-5.47</v>
+      </c>
+      <c r="O10" s="10">
+        <v>22.2</v>
       </c>
       <c r="P10" s="9">
-        <v>11.01</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>25.8</v>
+        <v>1.02</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>22.2</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="C11" s="7">
-        <v>299.5</v>
+        <v>264</v>
       </c>
       <c r="D11" s="7">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="E11" s="7">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="F11" s="8">
-        <v>32.5</v>
+        <v>-35.5</v>
       </c>
       <c r="G11" s="8">
-        <v>12.17</v>
+        <v>-11.85</v>
       </c>
       <c r="H11" s="9">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="I11" s="8">
-        <v>45</v>
-      </c>
-      <c r="J11" s="8">
-        <v>26.5</v>
+        <v>-19.7</v>
+      </c>
+      <c r="J11" s="10">
+        <v>14.3</v>
       </c>
       <c r="K11" s="9">
-        <v>9.93</v>
-      </c>
-      <c r="L11" s="8">
-        <v>27.2</v>
+        <v>11.01</v>
+      </c>
+      <c r="L11" s="10">
+        <v>25.8</v>
       </c>
       <c r="M11" s="9">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="N11" s="8">
-        <v>45</v>
-      </c>
-      <c r="O11" s="8">
-        <v>26.5</v>
+        <v>-19.7</v>
+      </c>
+      <c r="O11" s="10">
+        <v>14.3</v>
       </c>
       <c r="P11" s="9">
-        <v>9.93</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>27.2</v>
+        <v>11.01</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>25.8</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>218.5</v>
+        <v>269</v>
       </c>
       <c r="C12" s="7">
-        <v>267</v>
+        <v>299.5</v>
       </c>
       <c r="D12" s="7">
-        <v>287</v>
+        <v>327</v>
       </c>
       <c r="E12" s="7">
-        <v>205</v>
-      </c>
-      <c r="F12" s="8">
-        <v>48</v>
-      </c>
-      <c r="G12" s="8">
-        <v>21.92</v>
+        <v>237</v>
+      </c>
+      <c r="F12" s="10">
+        <v>32.5</v>
+      </c>
+      <c r="G12" s="10">
+        <v>12.17</v>
       </c>
       <c r="H12" s="9">
-        <v>0.92500000000000004</v>
+        <v>1.34</v>
       </c>
       <c r="I12" s="10">
-        <v>-0.66</v>
-      </c>
-      <c r="J12" s="8">
-        <v>18.100000000000001</v>
+        <v>45</v>
+      </c>
+      <c r="J12" s="10">
+        <v>26.5</v>
       </c>
       <c r="K12" s="9">
-        <v>8.59</v>
-      </c>
-      <c r="L12" s="8">
-        <v>27.3</v>
+        <v>9.93</v>
+      </c>
+      <c r="L12" s="10">
+        <v>27.2</v>
       </c>
       <c r="M12" s="9">
-        <v>0.92500000000000004</v>
+        <v>1.34</v>
       </c>
       <c r="N12" s="10">
-        <v>-0.66</v>
-      </c>
-      <c r="O12" s="8">
-        <v>18.100000000000001</v>
+        <v>45</v>
+      </c>
+      <c r="O12" s="10">
+        <v>26.5</v>
       </c>
       <c r="P12" s="9">
-        <v>8.59</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>27.3</v>
+        <v>9.93</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>27.2</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>261</v>
+        <v>218.5</v>
       </c>
       <c r="C13" s="7">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="D13" s="7">
-        <v>266.5</v>
+        <v>287</v>
       </c>
       <c r="E13" s="7">
-        <v>201.5</v>
+        <v>205</v>
       </c>
       <c r="F13" s="10">
-        <v>-40</v>
+        <v>48</v>
       </c>
       <c r="G13" s="10">
-        <v>-15.44</v>
+        <v>21.92</v>
       </c>
       <c r="H13" s="9">
-        <v>0.93100000000000005</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="I13" s="8">
-        <v>4.9800000000000004</v>
-      </c>
-      <c r="J13" s="8">
-        <v>20</v>
+        <v>-0.66</v>
+      </c>
+      <c r="J13" s="10">
+        <v>18.100000000000001</v>
       </c>
       <c r="K13" s="9">
-        <v>7.67</v>
-      </c>
-      <c r="L13" s="8">
-        <v>28.5</v>
+        <v>8.59</v>
+      </c>
+      <c r="L13" s="10">
+        <v>27.3</v>
       </c>
       <c r="M13" s="9">
-        <v>0.93100000000000005</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="N13" s="8">
-        <v>4.9800000000000004</v>
-      </c>
-      <c r="O13" s="8">
-        <v>20</v>
+        <v>-0.66</v>
+      </c>
+      <c r="O13" s="10">
+        <v>18.100000000000001</v>
       </c>
       <c r="P13" s="9">
-        <v>7.67</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>28.5</v>
+        <v>8.59</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>27.3</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>375</v>
+        <v>261</v>
       </c>
       <c r="C14" s="7">
-        <v>259</v>
+        <v>219</v>
       </c>
       <c r="D14" s="7">
-        <v>386</v>
+        <v>266.5</v>
       </c>
       <c r="E14" s="7">
-        <v>235</v>
-      </c>
-      <c r="F14" s="10">
-        <v>-116</v>
-      </c>
-      <c r="G14" s="10">
-        <v>-30.93</v>
+        <v>201.5</v>
+      </c>
+      <c r="F14" s="8">
+        <v>-40</v>
+      </c>
+      <c r="G14" s="8">
+        <v>-15.44</v>
       </c>
       <c r="H14" s="9">
-        <v>0.88700000000000001</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="I14" s="10">
-        <v>-2.72</v>
-      </c>
-      <c r="J14" s="8">
-        <v>30.9</v>
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="J14" s="10">
+        <v>20</v>
       </c>
       <c r="K14" s="9">
-        <v>6.74</v>
-      </c>
-      <c r="L14" s="8">
-        <v>29.7</v>
+        <v>7.67</v>
+      </c>
+      <c r="L14" s="10">
+        <v>28.5</v>
       </c>
       <c r="M14" s="9">
-        <v>0.88700000000000001</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="N14" s="10">
-        <v>-2.72</v>
-      </c>
-      <c r="O14" s="8">
-        <v>30.9</v>
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="O14" s="10">
+        <v>20</v>
       </c>
       <c r="P14" s="9">
-        <v>6.74</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>29.7</v>
+        <v>7.67</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>28.5</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="C15" s="7">
-        <v>375</v>
+        <v>259</v>
       </c>
       <c r="D15" s="7">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="E15" s="7">
-        <v>290</v>
+        <v>235</v>
       </c>
       <c r="F15" s="8">
-        <v>68</v>
+        <v>-116</v>
       </c>
       <c r="G15" s="8">
-        <v>22.15</v>
+        <v>-30.93</v>
       </c>
       <c r="H15" s="9">
-        <v>0.91100000000000003</v>
-      </c>
-      <c r="I15" s="10">
-        <v>-6.94</v>
-      </c>
-      <c r="J15" s="8">
-        <v>27.9</v>
+        <v>0.88700000000000001</v>
+      </c>
+      <c r="I15" s="8">
+        <v>-2.72</v>
+      </c>
+      <c r="J15" s="10">
+        <v>30.9</v>
       </c>
       <c r="K15" s="9">
-        <v>5.85</v>
-      </c>
-      <c r="L15" s="8">
-        <v>29.6</v>
+        <v>6.74</v>
+      </c>
+      <c r="L15" s="10">
+        <v>29.7</v>
       </c>
       <c r="M15" s="9">
-        <v>0.91100000000000003</v>
-      </c>
-      <c r="N15" s="10">
-        <v>-6.94</v>
-      </c>
-      <c r="O15" s="8">
-        <v>27.9</v>
+        <v>0.88700000000000001</v>
+      </c>
+      <c r="N15" s="8">
+        <v>-2.72</v>
+      </c>
+      <c r="O15" s="10">
+        <v>30.9</v>
       </c>
       <c r="P15" s="9">
-        <v>5.85</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>29.6</v>
+        <v>6.74</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>29.7</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
-        <v>186</v>
+        <v>318</v>
       </c>
       <c r="C16" s="7">
-        <v>307</v>
+        <v>375</v>
       </c>
       <c r="D16" s="7">
-        <v>360</v>
+        <v>427</v>
       </c>
       <c r="E16" s="7">
-        <v>160</v>
-      </c>
-      <c r="F16" s="8">
-        <v>117.5</v>
-      </c>
-      <c r="G16" s="8">
-        <v>62.01</v>
+        <v>290</v>
+      </c>
+      <c r="F16" s="10">
+        <v>68</v>
+      </c>
+      <c r="G16" s="10">
+        <v>22.15</v>
       </c>
       <c r="H16" s="9">
-        <v>0.97899999999999998</v>
+        <v>0.91100000000000003</v>
       </c>
       <c r="I16" s="8">
-        <v>11.3</v>
-      </c>
-      <c r="J16" s="8">
-        <v>39.9</v>
+        <v>-6.94</v>
+      </c>
+      <c r="J16" s="10">
+        <v>27.9</v>
       </c>
       <c r="K16" s="9">
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="L16" s="8">
-        <v>29.9</v>
+        <v>5.85</v>
+      </c>
+      <c r="L16" s="10">
+        <v>29.6</v>
       </c>
       <c r="M16" s="9">
-        <v>0.97899999999999998</v>
+        <v>0.91100000000000003</v>
       </c>
       <c r="N16" s="8">
-        <v>11.3</v>
-      </c>
-      <c r="O16" s="8">
-        <v>39.9</v>
+        <v>-6.94</v>
+      </c>
+      <c r="O16" s="10">
+        <v>27.9</v>
       </c>
       <c r="P16" s="9">
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>29.9</v>
+        <v>5.85</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>29.6</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="C17" s="7">
-        <v>189.5</v>
+        <v>307</v>
       </c>
       <c r="D17" s="7">
-        <v>205</v>
+        <v>360</v>
       </c>
       <c r="E17" s="7">
-        <v>145</v>
-      </c>
-      <c r="F17" s="8">
-        <v>123.5</v>
-      </c>
-      <c r="G17" s="8">
-        <v>187.12</v>
+        <v>160</v>
+      </c>
+      <c r="F17" s="10">
+        <v>117.5</v>
+      </c>
+      <c r="G17" s="10">
+        <v>62.01</v>
       </c>
       <c r="H17" s="9">
-        <v>0.88</v>
-      </c>
-      <c r="I17" s="8">
-        <v>22.1</v>
-      </c>
-      <c r="J17" s="8">
-        <v>33.6</v>
+        <v>0.97899999999999998</v>
+      </c>
+      <c r="I17" s="10">
+        <v>11.3</v>
+      </c>
+      <c r="J17" s="10">
+        <v>39.9</v>
       </c>
       <c r="K17" s="9">
-        <v>3.96</v>
-      </c>
-      <c r="L17" s="8">
-        <v>27.6</v>
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="L17" s="10">
+        <v>29.9</v>
       </c>
       <c r="M17" s="9">
-        <v>0.88</v>
-      </c>
-      <c r="N17" s="8">
-        <v>22.1</v>
-      </c>
-      <c r="O17" s="8">
-        <v>33.6</v>
+        <v>0.97899999999999998</v>
+      </c>
+      <c r="N17" s="10">
+        <v>11.3</v>
+      </c>
+      <c r="O17" s="10">
+        <v>39.9</v>
       </c>
       <c r="P17" s="9">
-        <v>3.96</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>27.6</v>
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>29.9</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>17</v>
+        <v>44317</v>
+      </c>
+      <c r="B18" s="7">
+        <v>145</v>
+      </c>
+      <c r="C18" s="7">
+        <v>189.5</v>
+      </c>
+      <c r="D18" s="7">
+        <v>205</v>
+      </c>
+      <c r="E18" s="7">
+        <v>145</v>
+      </c>
+      <c r="F18" s="10">
+        <v>123.5</v>
+      </c>
+      <c r="G18" s="10">
+        <v>187.12</v>
       </c>
       <c r="H18" s="9">
-        <v>0.72</v>
+        <v>0.88</v>
       </c>
       <c r="I18" s="10">
-        <v>-10.7</v>
-      </c>
-      <c r="J18" s="8">
-        <v>16.3</v>
+        <v>22.1</v>
+      </c>
+      <c r="J18" s="10">
+        <v>33.6</v>
       </c>
       <c r="K18" s="9">
-        <v>3.08</v>
-      </c>
-      <c r="L18" s="8">
-        <v>26</v>
+        <v>3.96</v>
+      </c>
+      <c r="L18" s="10">
+        <v>27.6</v>
       </c>
       <c r="M18" s="9">
-        <v>0.72</v>
+        <v>0.88</v>
       </c>
       <c r="N18" s="10">
-        <v>-10.7</v>
-      </c>
-      <c r="O18" s="8">
-        <v>16.3</v>
+        <v>22.1</v>
+      </c>
+      <c r="O18" s="10">
+        <v>33.6</v>
       </c>
       <c r="P18" s="9">
-        <v>3.08</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>26</v>
+        <v>3.96</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>27.6</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>17</v>
@@ -2147,33 +2147,86 @@
         <v>17</v>
       </c>
       <c r="H19" s="9">
+        <v>0.72</v>
+      </c>
+      <c r="I19" s="8">
+        <v>-10.7</v>
+      </c>
+      <c r="J19" s="10">
+        <v>16.3</v>
+      </c>
+      <c r="K19" s="9">
+        <v>3.08</v>
+      </c>
+      <c r="L19" s="10">
+        <v>26</v>
+      </c>
+      <c r="M19" s="9">
+        <v>0.72</v>
+      </c>
+      <c r="N19" s="8">
+        <v>-10.7</v>
+      </c>
+      <c r="O19" s="10">
+        <v>16.3</v>
+      </c>
+      <c r="P19" s="9">
+        <v>3.08</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>44256</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="9">
         <v>0.80700000000000005</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I20" s="10">
         <v>12.2</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J20" s="10">
         <v>27.1</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K20" s="9">
         <v>2.36</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L20" s="10">
         <v>29.3</v>
       </c>
-      <c r="M19" s="9">
+      <c r="M20" s="9">
         <v>0.80700000000000005</v>
       </c>
-      <c r="N19" s="8">
+      <c r="N20" s="10">
         <v>12.2</v>
       </c>
-      <c r="O19" s="8">
+      <c r="O20" s="10">
         <v>27.1</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P20" s="9">
         <v>2.36</v>
       </c>
-      <c r="Q19" s="8">
+      <c r="Q20" s="10">
         <v>29.3</v>
       </c>
     </row>
